--- a/InputData/bldgs/FoBObE/Frac of Bldgs Owned by Entity.xlsx
+++ b/InputData/bldgs/FoBObE/Frac of Bldgs Owned by Entity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28609"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anaxolt/Google Drive/2021/D.Development/TARGET_eps-us-3.2.1/InputData/bldgs/FoBObE/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rod\Downloads\MX\FoBObE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42948964-DC2E-EF45-BE8C-2124C736370B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A39513CA-5F4C-4DD0-89DC-024E7C760305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4080" yWindow="6000" windowWidth="29520" windowHeight="15000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,11 @@
     <definedName name="outputfrac_nonenergy">#REF!</definedName>
     <definedName name="outputfrac_other">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -36,6 +39,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -45,93 +50,129 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="74">
   <si>
+    <t>FoBObE Fraction of Buildings Owned by Entity</t>
+  </si>
+  <si>
     <t>Sources:</t>
   </si>
   <si>
+    <t>Residential &amp; Commercial</t>
+  </si>
+  <si>
+    <t>SENER - SIE Sistema de Información energética</t>
+  </si>
+  <si>
+    <t>Balance Nacional de Energía (BNE)</t>
+  </si>
+  <si>
+    <t>https://www.gob.mx/cms/uploads/attachment/file/977268/Balance_Nacional_de_Energ_a_2023.FINAL06.02.2025.1.pdf</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>In the output tab, we show more decimal places than the source data</t>
+  </si>
+  <si>
+    <t>provide in order to avoid rounding error in Vensim (each column must</t>
+  </si>
+  <si>
+    <t>add to 1).</t>
+  </si>
+  <si>
     <t>Residential</t>
   </si>
   <si>
+    <t>2.1.14</t>
+  </si>
+  <si>
+    <t>2005 Residential Delivered Energy Consumption Intensities, by Ownership of Unit</t>
+  </si>
+  <si>
+    <t>Per Square</t>
+  </si>
+  <si>
+    <t>Per Household</t>
+  </si>
+  <si>
+    <t>Percent of</t>
+  </si>
+  <si>
+    <t>Ownership</t>
+  </si>
+  <si>
+    <t>Foot (thousand Btu)</t>
+  </si>
+  <si>
+    <t>(1)</t>
+  </si>
+  <si>
+    <t>(million Btu)</t>
+  </si>
+  <si>
+    <t>Members (million Btu)</t>
+  </si>
+  <si>
+    <t>Total Consumption</t>
+  </si>
+  <si>
+    <t>Owned</t>
+  </si>
+  <si>
+    <t>Rented</t>
+  </si>
+  <si>
+    <t>Public Housing</t>
+  </si>
+  <si>
+    <t>Not Public Housing</t>
+  </si>
+  <si>
+    <t>Note(s):</t>
+  </si>
+  <si>
+    <t>1) Energy consumption per square foot was calculated using estimates of average heated floor space per household. According to the 2005 Residential Energy Consumption Survey (RECS), the average heated floor space per household in the U.S. was 1,618 square feet. Average total floor space, which includes garages, attics and unfinished basements, equaled 2,309 square feet.</t>
+  </si>
+  <si>
+    <t>Source(s):</t>
+  </si>
+  <si>
+    <t>EIA, 2005 Residential Energy Consumption Survey, Oct. 2008</t>
+  </si>
+  <si>
+    <t>Converting percentage of energy consumption (by ownership) to percentage of floor area (by ownership):</t>
+  </si>
+  <si>
+    <t>Floor Area</t>
+  </si>
+  <si>
+    <t>Assumptions:</t>
+  </si>
+  <si>
+    <t>All owner-occupied housing belongs to consumers.</t>
+  </si>
+  <si>
+    <t>All public housing belongs to government.</t>
+  </si>
+  <si>
+    <t>Fraction of rental housing that is owned by an individual (consumers):</t>
+  </si>
+  <si>
+    <t>Fraction of rental housing that is owned by a company (industry):</t>
+  </si>
+  <si>
+    <t>government</t>
+  </si>
+  <si>
+    <t>industry</t>
+  </si>
+  <si>
+    <t>consumers</t>
+  </si>
+  <si>
     <t>Commercial</t>
   </si>
   <si>
-    <t>2.1.14</t>
-  </si>
-  <si>
-    <t>2005 Residential Delivered Energy Consumption Intensities, by Ownership of Unit</t>
-  </si>
-  <si>
-    <t>Per Square</t>
-  </si>
-  <si>
-    <t>Per Household</t>
-  </si>
-  <si>
-    <t>Percent of</t>
-  </si>
-  <si>
-    <t>Ownership</t>
-  </si>
-  <si>
-    <t>Foot (thousand Btu)</t>
-  </si>
-  <si>
-    <t>(1)</t>
-  </si>
-  <si>
-    <t>(million Btu)</t>
-  </si>
-  <si>
-    <t>Members (million Btu)</t>
-  </si>
-  <si>
-    <t>Total Consumption</t>
-  </si>
-  <si>
-    <t>Owned</t>
-  </si>
-  <si>
-    <t>Rented</t>
-  </si>
-  <si>
-    <t>Public Housing</t>
-  </si>
-  <si>
-    <t>Not Public Housing</t>
-  </si>
-  <si>
-    <t>Note(s):</t>
-  </si>
-  <si>
-    <t>1) Energy consumption per square foot was calculated using estimates of average heated floor space per household. According to the 2005 Residential Energy Consumption Survey (RECS), the average heated floor space per household in the U.S. was 1,618 square feet. Average total floor space, which includes garages, attics and unfinished basements, equaled 2,309 square feet.</t>
-  </si>
-  <si>
-    <t>Source(s):</t>
-  </si>
-  <si>
-    <t>EIA, 2005 Residential Energy Consumption Survey, Oct. 2008</t>
-  </si>
-  <si>
-    <t>Floor Area</t>
-  </si>
-  <si>
-    <t>Assumptions:</t>
-  </si>
-  <si>
-    <t>Fraction of rental housing that is owned by a company (industry):</t>
-  </si>
-  <si>
-    <t>government</t>
-  </si>
-  <si>
-    <t>industry</t>
-  </si>
-  <si>
-    <t>consumers</t>
-  </si>
-  <si>
-    <t>Converting percentage of energy consumption (by ownership) to percentage of floor area (by ownership):</t>
-  </si>
-  <si>
     <t>3.2.3</t>
   </si>
   <si>
@@ -186,16 +227,34 @@
     <t>EIA, Commercial Building Characteristics 2003, June 2006, Table C1.</t>
   </si>
   <si>
-    <t>All owner-occupied housing belongs to consumers.</t>
-  </si>
-  <si>
-    <t>All public housing belongs to government.</t>
-  </si>
-  <si>
-    <t>Fraction of rental housing that is owned by an individual (consumers):</t>
-  </si>
-  <si>
-    <t>FoBObE Fraction of Buildings Owned by Entity</t>
+    <t>SPLIT EDIFICIOS RESIDENCIALES</t>
+  </si>
+  <si>
+    <t>SPLIT EDIFICIOS COMERCIALES</t>
+  </si>
+  <si>
+    <t>PUBLICO</t>
+  </si>
+  <si>
+    <t>PRIVADO</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Balance Nacional de Energía 2017-2019</t>
+  </si>
+  <si>
+    <t>Residencial</t>
+  </si>
+  <si>
+    <t>Comercial</t>
+  </si>
+  <si>
+    <t>Público</t>
+  </si>
+  <si>
+    <t>Ownership by Cash Flow Entity (dimensionless)</t>
   </si>
   <si>
     <t>Urban Residential</t>
@@ -204,67 +263,13 @@
     <t>Rural Residential</t>
   </si>
   <si>
+    <t>domestic industries</t>
+  </si>
+  <si>
+    <t>labor and consumers</t>
+  </si>
+  <si>
     <t>foreign entities</t>
-  </si>
-  <si>
-    <t>labor and consumers</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>In the output tab, we show more decimal places than the source data</t>
-  </si>
-  <si>
-    <t>add to 1).</t>
-  </si>
-  <si>
-    <t>provide in order to avoid rounding error in Vensim (each column must</t>
-  </si>
-  <si>
-    <t>Ownership by Cash Flow Entity (dimensionless)</t>
-  </si>
-  <si>
-    <t>domestic industries</t>
-  </si>
-  <si>
-    <t>Balance Nacional de Energía (BNE)</t>
-  </si>
-  <si>
-    <t>http://www.cie.unam.mx/~rbb/ERyS2013-1/BalanceNacionaldeEnergia2010_2.pdf</t>
-  </si>
-  <si>
-    <t>Residential &amp; Commercial</t>
-  </si>
-  <si>
-    <t>SPLIT EDIFICIOS COMERCIALES</t>
-  </si>
-  <si>
-    <t>PUBLICO</t>
-  </si>
-  <si>
-    <t>PRIVADO</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>SENER - SIE Sistema de Información energética</t>
-  </si>
-  <si>
-    <t>Balance Nacional de Energía 2017-2019</t>
-  </si>
-  <si>
-    <t>SPLIT EDIFICIOS RESIDENCIALES</t>
-  </si>
-  <si>
-    <t>Residencial</t>
-  </si>
-  <si>
-    <t>Comercial</t>
-  </si>
-  <si>
-    <t>Público</t>
   </si>
 </sst>
 </file>
@@ -277,7 +282,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.00000000"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -582,7 +587,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -594,16 +599,15 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -613,15 +617,15 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -654,30 +658,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -689,44 +686,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
@@ -737,12 +699,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Hyperlink" xfId="3" builtinId="8"/>
+    <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
+    <cellStyle name="Millares" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Per cent" xfId="2" builtinId="5"/>
+    <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -758,9 +751,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -798,9 +791,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -833,26 +826,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -885,26 +861,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1079,64 +1038,64 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.6640625" customWidth="1"/>
-    <col min="2" max="2" width="67.1640625" customWidth="1"/>
-    <col min="3" max="3" width="68.5" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="2" max="2" width="67.140625" customWidth="1"/>
+    <col min="3" max="3" width="68.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="B5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="B6" s="2">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="B7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="B8" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1148,41 +1107,41 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="22.6640625" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="63" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="63"/>
-      <c r="L3" s="63"/>
-      <c r="M3" s="63"/>
+        <v>11</v>
+      </c>
+      <c r="B3" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="69"/>
+      <c r="K3" s="69"/>
+      <c r="L3" s="69"/>
+      <c r="M3" s="69"/>
       <c r="N3" s="6"/>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
       <c r="Q3" s="7"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17">
       <c r="A4" s="8"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -1201,181 +1160,181 @@
       <c r="P4" s="9"/>
       <c r="Q4" s="10"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17">
       <c r="A5" s="8"/>
       <c r="B5" s="9"/>
-      <c r="C5" s="64" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="64"/>
-      <c r="E5" s="64"/>
+      <c r="C5" s="63" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="63"/>
+      <c r="E5" s="63"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="64" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
+      <c r="G5" s="63" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="63"/>
+      <c r="I5" s="63"/>
       <c r="J5" s="9"/>
-      <c r="K5" s="64" t="s">
-        <v>6</v>
-      </c>
-      <c r="L5" s="64"/>
-      <c r="M5" s="64"/>
+      <c r="K5" s="63" t="s">
+        <v>14</v>
+      </c>
+      <c r="L5" s="63"/>
+      <c r="M5" s="63"/>
       <c r="N5" s="9"/>
-      <c r="O5" s="65" t="s">
-        <v>7</v>
-      </c>
-      <c r="P5" s="65"/>
-      <c r="Q5" s="66"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="O5" s="63" t="s">
+        <v>15</v>
+      </c>
+      <c r="P5" s="63"/>
+      <c r="Q5" s="64"/>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" s="11" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B6" s="9"/>
-      <c r="C6" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
+      <c r="C6" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
       <c r="F6" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="67" t="s">
-        <v>11</v>
-      </c>
-      <c r="H6" s="67"/>
-      <c r="I6" s="67"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="L6" s="67"/>
-      <c r="M6" s="67"/>
-      <c r="N6" s="14"/>
-      <c r="O6" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="P6" s="67"/>
-      <c r="Q6" s="68"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A7" s="15" t="s">
-        <v>14</v>
+        <v>18</v>
+      </c>
+      <c r="G6" s="65" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="65" t="s">
+        <v>20</v>
+      </c>
+      <c r="L6" s="65"/>
+      <c r="M6" s="65"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="65" t="s">
+        <v>21</v>
+      </c>
+      <c r="P6" s="65"/>
+      <c r="Q6" s="66"/>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="14" t="s">
+        <v>22</v>
       </c>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
-      <c r="D7" s="16">
+      <c r="D7" s="15">
         <v>54.92</v>
       </c>
-      <c r="E7" s="17"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="16">
+      <c r="E7" s="16"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="15">
         <v>104.45</v>
       </c>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="16">
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="15">
         <v>40.328185328185334</v>
       </c>
       <c r="M7" s="9"/>
       <c r="N7" s="9"/>
       <c r="O7" s="9"/>
-      <c r="P7" s="18">
+      <c r="P7" s="17">
         <v>0.7816091954022989</v>
       </c>
       <c r="Q7" s="10"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A8" s="15" t="s">
-        <v>15</v>
+    <row r="8" spans="1:17">
+      <c r="A8" s="14" t="s">
+        <v>23</v>
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
-      <c r="D8" s="16">
+      <c r="D8" s="15">
         <v>77.42</v>
       </c>
-      <c r="E8" s="17"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16">
+      <c r="E8" s="16"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15">
         <v>71.67</v>
       </c>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="16">
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="15">
         <v>28.44047619047619</v>
       </c>
       <c r="M8" s="9"/>
       <c r="N8" s="9"/>
       <c r="O8" s="9"/>
-      <c r="P8" s="18">
+      <c r="P8" s="17">
         <v>0.21839080459770113</v>
       </c>
       <c r="Q8" s="10"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A9" s="19" t="s">
-        <v>16</v>
+    <row r="9" spans="1:17">
+      <c r="A9" s="18" t="s">
+        <v>24</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
-      <c r="D9" s="16">
+      <c r="D9" s="15">
         <v>75.709999999999994</v>
       </c>
-      <c r="E9" s="17"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16">
+      <c r="E9" s="16"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15">
         <v>62.67</v>
       </c>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="16">
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="15">
         <v>28.747706422018346</v>
       </c>
       <c r="M9" s="9"/>
       <c r="N9" s="9"/>
       <c r="O9" s="9"/>
-      <c r="P9" s="20">
+      <c r="P9" s="19">
         <v>2.4904214559386975E-2</v>
       </c>
       <c r="Q9" s="10"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A10" s="19" t="s">
-        <v>17</v>
+    <row r="10" spans="1:17">
+      <c r="A10" s="18" t="s">
+        <v>25</v>
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
-      <c r="D10" s="16">
+      <c r="D10" s="15">
         <v>77.650000000000006</v>
       </c>
-      <c r="E10" s="17"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16">
+      <c r="E10" s="16"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15">
         <v>73.040000000000006</v>
       </c>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="16">
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="15">
         <v>28.420233463035025</v>
       </c>
       <c r="M10" s="9"/>
       <c r="N10" s="9"/>
       <c r="O10" s="9"/>
-      <c r="P10" s="21">
+      <c r="P10" s="20">
         <v>0.1934865900383142</v>
       </c>
       <c r="Q10" s="10"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17">
       <c r="A11" s="8"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -1391,12 +1350,12 @@
       <c r="M11" s="9"/>
       <c r="N11" s="9"/>
       <c r="O11" s="9"/>
-      <c r="P11" s="18">
+      <c r="P11" s="17">
         <v>1</v>
       </c>
       <c r="Q11" s="10"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17">
       <c r="A12" s="8"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -1412,15 +1371,15 @@
       <c r="M12" s="9"/>
       <c r="N12" s="9"/>
       <c r="O12" s="9"/>
-      <c r="P12" s="22"/>
+      <c r="P12" s="21"/>
       <c r="Q12" s="10"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A13" s="23" t="s">
-        <v>18</v>
+    <row r="13" spans="1:17">
+      <c r="A13" s="22" t="s">
+        <v>26</v>
       </c>
       <c r="B13" s="59" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C13" s="59"/>
       <c r="D13" s="59"/>
@@ -1438,8 +1397,8 @@
       <c r="P13" s="59"/>
       <c r="Q13" s="60"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A14" s="23"/>
+    <row r="14" spans="1:17">
+      <c r="A14" s="22"/>
       <c r="B14" s="59"/>
       <c r="C14" s="59"/>
       <c r="D14" s="59"/>
@@ -1457,8 +1416,8 @@
       <c r="P14" s="59"/>
       <c r="Q14" s="60"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A15" s="23"/>
+    <row r="15" spans="1:17">
+      <c r="A15" s="22"/>
       <c r="B15" s="59"/>
       <c r="C15" s="59"/>
       <c r="D15" s="59"/>
@@ -1476,12 +1435,12 @@
       <c r="P15" s="59"/>
       <c r="Q15" s="60"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A16" s="24" t="s">
-        <v>20</v>
+    <row r="16" spans="1:17">
+      <c r="A16" s="23" t="s">
+        <v>28</v>
       </c>
       <c r="B16" s="61" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C16" s="61"/>
       <c r="D16" s="61"/>
@@ -1499,127 +1458,127 @@
       <c r="P16" s="61"/>
       <c r="Q16" s="62"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="B20" s="1" t="str">
         <f>A6</f>
         <v>Ownership</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="B21" t="str">
         <f t="shared" ref="B21:B23" si="0">A7</f>
         <v>Owned</v>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="25">
         <f>(P7/D7)/SUM(P$7/D$7,P$9/D$9,P$10/D$10)</f>
         <v>0.83458607438155852</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="B22" t="str">
         <f t="shared" si="0"/>
         <v>Rented</v>
       </c>
-      <c r="C22" s="26"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B23" s="25" t="str">
+      <c r="C22" s="25"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="B23" s="24" t="str">
         <f t="shared" si="0"/>
         <v>Public Housing</v>
       </c>
-      <c r="C23" s="26">
+      <c r="C23" s="25">
         <f>(P9/D9)/SUM(P$7/D$7,P$9/D$9,P$10/D$10)</f>
         <v>1.9289972368294446E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B24" s="25" t="str">
+    <row r="24" spans="1:7">
+      <c r="B24" s="24" t="str">
         <f>A10</f>
         <v>Not Public Housing</v>
       </c>
-      <c r="C24" s="26">
+      <c r="C24" s="25">
         <f>(P10/D10)/SUM(P$7/D$7,P$9/D$9,P$10/D$10)</f>
         <v>0.14612395325014693</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C25" s="26">
+    <row r="25" spans="1:7">
+      <c r="C25" s="25">
         <f>SUM(C21:C24)</f>
         <v>0.99999999999999989</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="B28" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="B29" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="B30" t="s">
-        <v>49</v>
-      </c>
-      <c r="G30" s="27">
+        <v>35</v>
+      </c>
+      <c r="G30" s="26">
         <v>0.75</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="B31" t="s">
-        <v>24</v>
-      </c>
-      <c r="G31" s="27">
+        <v>36</v>
+      </c>
+      <c r="G31" s="26">
         <f>1-G30</f>
         <v>0.25</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B33" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="C33" s="29" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B34" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="C34" s="32">
+    <row r="32" spans="1:7" ht="15.75" thickBot="1"/>
+    <row r="33" spans="2:3">
+      <c r="B33" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="28" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3">
+      <c r="B34" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" s="31">
         <f>C23</f>
         <v>1.9289972368294446E-2</v>
       </c>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B35" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="C35" s="33">
+    <row r="35" spans="2:3">
+      <c r="B35" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="C35" s="32">
         <f>C24*G31</f>
         <v>3.6530988312536733E-2</v>
       </c>
     </row>
-    <row r="36" spans="2:3" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="C36" s="34">
+    <row r="36" spans="2:3" ht="15.75" thickBot="1">
+      <c r="B36" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="33">
         <f>C21+(C24*G30)</f>
         <v>0.94417903931916869</v>
       </c>
@@ -1645,387 +1604,387 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Q22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="13.5" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A3" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="37"/>
-      <c r="J3" s="37"/>
-      <c r="K3" s="37"/>
-      <c r="L3" s="37"/>
-      <c r="M3" s="37"/>
-      <c r="N3" s="37"/>
-      <c r="O3" s="37"/>
-      <c r="P3" s="37"/>
-      <c r="Q3" s="38"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A4" s="39"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="40"/>
-      <c r="L4" s="40"/>
-      <c r="M4" s="40"/>
-      <c r="N4" s="40"/>
-      <c r="O4" s="40"/>
-      <c r="P4" s="40"/>
-      <c r="Q4" s="41"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
+      <c r="A3" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="7"/>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4" s="8"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="10"/>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="37"/>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="38">
+        <v>0.4010403803408249</v>
+      </c>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="39" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="40">
+        <v>0.76285811311434926</v>
+      </c>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="10"/>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="38">
+        <v>0.25114225734749318</v>
+      </c>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="41" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="19">
+        <v>0.36414855519881451</v>
+      </c>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="10"/>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="38">
+        <v>0.11578476166954804</v>
+      </c>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="19">
+        <v>0.36913435416152135</v>
+      </c>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="10"/>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="38">
+        <v>0.15567115337120277</v>
+      </c>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="19">
+        <v>2.9575203754013336E-2</v>
+      </c>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="10"/>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="A10" s="42" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="43">
+        <v>7.6361447270931096E-2</v>
+      </c>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="40">
+        <v>0.23714188688565077</v>
+      </c>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="9"/>
+      <c r="Q10" s="10"/>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="38">
+        <v>1</v>
+      </c>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="38">
+        <v>3.0192640158063718E-2</v>
+      </c>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="10"/>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="A12" s="8"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="H12" s="44"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="38">
+        <v>4.8779945665596444E-2</v>
+      </c>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="10"/>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="A13" s="8"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="43">
+        <v>0.14816930106199061</v>
+      </c>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="10"/>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="A14" s="8"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="19">
+        <v>1</v>
+      </c>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="10"/>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15" s="8"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="19"/>
+      <c r="Q15" s="10"/>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="67" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="67"/>
+      <c r="D16" s="67"/>
+      <c r="E16" s="67"/>
+      <c r="F16" s="67"/>
+      <c r="G16" s="67"/>
+      <c r="H16" s="67"/>
+      <c r="I16" s="67"/>
+      <c r="J16" s="67"/>
+      <c r="K16" s="67"/>
+      <c r="L16" s="67"/>
+      <c r="M16" s="67"/>
+      <c r="N16" s="67"/>
+      <c r="O16" s="67"/>
+      <c r="P16" s="67"/>
+      <c r="Q16" s="68"/>
+    </row>
+    <row r="18" spans="2:3" ht="15.75" thickBot="1"/>
+    <row r="19" spans="2:3">
+      <c r="B19" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="43" t="s">
-        <v>8</v>
-      </c>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
-      <c r="L5" s="40"/>
-      <c r="M5" s="40"/>
-      <c r="N5" s="40"/>
-      <c r="O5" s="40"/>
-      <c r="P5" s="40"/>
-      <c r="Q5" s="44"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A6" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="45">
-        <v>0.4010403803408249</v>
-      </c>
-      <c r="E6" s="40"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="46" t="s">
-        <v>33</v>
-      </c>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
-      <c r="K6" s="47">
-        <v>0.76285811311434926</v>
-      </c>
-      <c r="L6" s="40"/>
-      <c r="M6" s="40"/>
-      <c r="N6" s="40"/>
-      <c r="O6" s="40"/>
-      <c r="P6" s="40"/>
-      <c r="Q6" s="41"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A7" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="40"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="45">
-        <v>0.25114225734749318</v>
-      </c>
-      <c r="E7" s="40"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" s="40"/>
-      <c r="I7" s="40"/>
-      <c r="J7" s="40"/>
-      <c r="K7" s="49">
-        <v>0.36414855519881451</v>
-      </c>
-      <c r="L7" s="40"/>
-      <c r="M7" s="40"/>
-      <c r="N7" s="40"/>
-      <c r="O7" s="40"/>
-      <c r="P7" s="40"/>
-      <c r="Q7" s="41"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A8" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="40"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="45">
-        <v>0.11578476166954804</v>
-      </c>
-      <c r="E8" s="40"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="48" t="s">
+    </row>
+    <row r="20" spans="2:3">
+      <c r="B20" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="40"/>
-      <c r="K8" s="49">
-        <v>0.36913435416152135</v>
-      </c>
-      <c r="L8" s="40"/>
-      <c r="M8" s="40"/>
-      <c r="N8" s="40"/>
-      <c r="O8" s="40"/>
-      <c r="P8" s="40"/>
-      <c r="Q8" s="41"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A9" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="40"/>
-      <c r="C9" s="40"/>
-      <c r="D9" s="45">
-        <v>0.15567115337120277</v>
-      </c>
-      <c r="E9" s="40"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="48" t="s">
-        <v>39</v>
-      </c>
-      <c r="H9" s="40"/>
-      <c r="I9" s="40"/>
-      <c r="J9" s="40"/>
-      <c r="K9" s="49">
-        <v>2.9575203754013336E-2</v>
-      </c>
-      <c r="L9" s="40"/>
-      <c r="M9" s="40"/>
-      <c r="N9" s="40"/>
-      <c r="O9" s="40"/>
-      <c r="P9" s="40"/>
-      <c r="Q9" s="41"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A10" s="50" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="40"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="51">
-        <v>7.6361447270931096E-2</v>
-      </c>
-      <c r="E10" s="40"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="46" t="s">
-        <v>41</v>
-      </c>
-      <c r="H10" s="40"/>
-      <c r="I10" s="40"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="47">
-        <v>0.23714188688565077</v>
-      </c>
-      <c r="L10" s="40"/>
-      <c r="M10" s="40"/>
-      <c r="N10" s="40"/>
-      <c r="O10" s="40"/>
-      <c r="P10" s="40"/>
-      <c r="Q10" s="41"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A11" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="B11" s="40"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="45">
-        <v>1</v>
-      </c>
-      <c r="E11" s="40"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="48" t="s">
-        <v>43</v>
-      </c>
-      <c r="H11" s="40"/>
-      <c r="I11" s="40"/>
-      <c r="J11" s="40"/>
-      <c r="K11" s="45">
-        <v>3.0192640158063718E-2</v>
-      </c>
-      <c r="L11" s="40"/>
-      <c r="M11" s="40"/>
-      <c r="N11" s="40"/>
-      <c r="O11" s="40"/>
-      <c r="P11" s="40"/>
-      <c r="Q11" s="41"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A12" s="39"/>
-      <c r="B12" s="40"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="48" t="s">
-        <v>44</v>
-      </c>
-      <c r="H12" s="52"/>
-      <c r="I12" s="40"/>
-      <c r="J12" s="40"/>
-      <c r="K12" s="45">
-        <v>4.8779945665596444E-2</v>
-      </c>
-      <c r="L12" s="40"/>
-      <c r="M12" s="40"/>
-      <c r="N12" s="40"/>
-      <c r="O12" s="40"/>
-      <c r="P12" s="40"/>
-      <c r="Q12" s="41"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A13" s="39"/>
-      <c r="B13" s="40"/>
-      <c r="C13" s="40"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="53" t="s">
-        <v>45</v>
-      </c>
-      <c r="H13" s="40"/>
-      <c r="I13" s="40"/>
-      <c r="J13" s="40"/>
-      <c r="K13" s="51">
-        <v>0.14816930106199061</v>
-      </c>
-      <c r="L13" s="40"/>
-      <c r="M13" s="40"/>
-      <c r="N13" s="40"/>
-      <c r="O13" s="40"/>
-      <c r="P13" s="49"/>
-      <c r="Q13" s="41"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A14" s="39"/>
-      <c r="B14" s="40"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="H14" s="40"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="40"/>
-      <c r="K14" s="49">
-        <v>1</v>
-      </c>
-      <c r="L14" s="40"/>
-      <c r="M14" s="40"/>
-      <c r="N14" s="40"/>
-      <c r="O14" s="40"/>
-      <c r="P14" s="49"/>
-      <c r="Q14" s="41"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A15" s="39"/>
-      <c r="B15" s="40"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="40"/>
-      <c r="I15" s="40"/>
-      <c r="J15" s="49"/>
-      <c r="K15" s="40"/>
-      <c r="L15" s="40"/>
-      <c r="M15" s="40"/>
-      <c r="N15" s="40"/>
-      <c r="O15" s="40"/>
-      <c r="P15" s="49"/>
-      <c r="Q15" s="41"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A16" s="54" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="69" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="69"/>
-      <c r="D16" s="69"/>
-      <c r="E16" s="69"/>
-      <c r="F16" s="69"/>
-      <c r="G16" s="69"/>
-      <c r="H16" s="69"/>
-      <c r="I16" s="69"/>
-      <c r="J16" s="69"/>
-      <c r="K16" s="69"/>
-      <c r="L16" s="69"/>
-      <c r="M16" s="69"/>
-      <c r="N16" s="69"/>
-      <c r="O16" s="69"/>
-      <c r="P16" s="69"/>
-      <c r="Q16" s="70"/>
-    </row>
-    <row r="18" spans="2:3" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B19" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="29" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B20" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="32">
+      <c r="C20" s="31">
         <f>K10</f>
         <v>0.23714188688565077</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B21" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="33">
+    <row r="21" spans="2:3">
+      <c r="B21" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="32">
         <f>K6</f>
         <v>0.76285811311434926</v>
       </c>
     </row>
-    <row r="22" spans="2:3" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="34">
+    <row r="22" spans="2:3" ht="15.75" thickBot="1">
+      <c r="B22" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="33">
         <v>0</v>
       </c>
     </row>
@@ -2039,92 +1998,93 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4650B03-E0A3-5D4F-B77E-09651BD6C4D7}">
-  <dimension ref="B2:H11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="B2:J11"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B2" s="71" t="s">
-        <v>70</v>
-      </c>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="F2" s="71" t="s">
-        <v>64</v>
-      </c>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B3" s="73" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" s="74">
+    <row r="2" spans="2:10">
+      <c r="B2" s="50" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="F2" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+    </row>
+    <row r="3" spans="2:10">
+      <c r="B3" s="52" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="53">
         <f>SUM(D11:F11)/3-G3</f>
-        <v>6.1868000000000016</v>
-      </c>
-      <c r="D3" s="74">
+        <v>4.9179999999999993</v>
+      </c>
+      <c r="D3" s="53">
         <f>C3/C5</f>
-        <v>2.6842318085027003E-2</v>
-      </c>
-      <c r="F3" s="73" t="s">
-        <v>65</v>
-      </c>
-      <c r="G3" s="74">
+        <v>2.1455557591463146E-2</v>
+      </c>
+      <c r="F3" s="52" t="s">
+        <v>61</v>
+      </c>
+      <c r="G3" s="53">
         <f>SUM(D11:F11)*0.8/3</f>
-        <v>24.747199999999996</v>
-      </c>
-      <c r="H3" s="74">
+        <v>19.672000000000001</v>
+      </c>
+      <c r="H3" s="53">
         <f>G3/G5</f>
-        <v>0.15861731280438049</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="75" t="s">
-        <v>66</v>
-      </c>
-      <c r="C4" s="76">
+        <v>0.22575511827891179</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" ht="15.75" thickBot="1">
+      <c r="B4" s="54" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="55">
         <f>SUM(D9:F9)/3</f>
         <v>224.29999999999998</v>
       </c>
-      <c r="D4" s="76">
+      <c r="D4" s="55">
         <f>C4/C5</f>
-        <v>0.97315768191497298</v>
-      </c>
-      <c r="F4" s="75" t="s">
-        <v>66</v>
-      </c>
-      <c r="G4" s="74">
+        <v>0.97854444240853677</v>
+      </c>
+      <c r="F4" s="54" t="s">
+        <v>62</v>
+      </c>
+      <c r="G4" s="53">
         <f>SUM(D10:F10)/3</f>
-        <v>87.112666666666669</v>
-      </c>
-      <c r="H4" s="76">
+        <v>67.466666666666669</v>
+      </c>
+      <c r="H4" s="55">
         <f>G4/G5</f>
-        <v>0.5583491101171203</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B5" s="77" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" s="78">
+        <v>0.7742448817210883</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10">
+      <c r="B5" s="56" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="57">
         <f>C3+C4</f>
-        <v>230.48679999999999</v>
-      </c>
-      <c r="D5" s="77"/>
-      <c r="F5" s="77" t="s">
-        <v>67</v>
-      </c>
-      <c r="G5" s="78">
-        <v>156.01827797019999</v>
-      </c>
-      <c r="H5" s="77"/>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+        <v>229.21799999999999</v>
+      </c>
+      <c r="D5" s="56"/>
+      <c r="F5" s="56" t="s">
+        <v>63</v>
+      </c>
+      <c r="G5" s="57">
+        <f>SUM(G3:G4)</f>
+        <v>87.138666666666666</v>
+      </c>
+      <c r="H5" s="56"/>
+    </row>
+    <row r="7" spans="2:10">
       <c r="B7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10">
       <c r="D8" s="1">
         <v>2017</v>
       </c>
@@ -2134,57 +2094,99 @@
       <c r="F8" s="1">
         <v>2019</v>
       </c>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B9" s="79" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" s="79"/>
-      <c r="D9" s="79">
+      <c r="G8" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H8" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I8" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J8" s="1">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10">
+      <c r="B9" s="58" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="58"/>
+      <c r="D9" s="58">
         <v>212.95</v>
       </c>
-      <c r="E9" s="79">
-        <v>227.80199999999999</v>
-      </c>
-      <c r="F9" s="79">
-        <v>232.148</v>
-      </c>
-      <c r="G9" s="79"/>
-      <c r="H9" s="79"/>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B10" s="79" t="s">
-        <v>72</v>
-      </c>
-      <c r="C10" s="79"/>
-      <c r="D10" s="79">
-        <v>81.489999999999995</v>
-      </c>
-      <c r="E10" s="79">
-        <v>87.173000000000002</v>
-      </c>
-      <c r="F10" s="79">
-        <v>92.674999999999997</v>
-      </c>
-      <c r="G10" s="79"/>
-      <c r="H10" s="79"/>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B11" s="79" t="s">
-        <v>73</v>
-      </c>
-      <c r="C11" s="79"/>
-      <c r="D11" s="79">
-        <v>28.917000000000002</v>
-      </c>
-      <c r="E11" s="79">
-        <v>30.934000000000001</v>
-      </c>
-      <c r="F11" s="79">
-        <v>32.951000000000001</v>
-      </c>
-      <c r="G11" s="79"/>
-      <c r="H11" s="79"/>
+      <c r="E9" s="58">
+        <v>227.8</v>
+      </c>
+      <c r="F9" s="58">
+        <v>232.15</v>
+      </c>
+      <c r="G9" s="58">
+        <v>260.10000000000002</v>
+      </c>
+      <c r="H9" s="58">
+        <v>250.06</v>
+      </c>
+      <c r="I9" s="58">
+        <v>264.91000000000003</v>
+      </c>
+      <c r="J9" s="58">
+        <v>271.63</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10">
+      <c r="B10" s="58" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" s="58"/>
+      <c r="D10" s="58">
+        <v>68.13</v>
+      </c>
+      <c r="E10" s="58">
+        <v>66.17</v>
+      </c>
+      <c r="F10" s="58">
+        <v>68.099999999999994</v>
+      </c>
+      <c r="G10" s="58">
+        <v>65.8</v>
+      </c>
+      <c r="H10" s="58">
+        <v>71.990000000000009</v>
+      </c>
+      <c r="I10">
+        <v>80.177510985352882</v>
+      </c>
+      <c r="J10">
+        <v>77.91580925432757</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10">
+      <c r="B11" s="58" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="58"/>
+      <c r="D11" s="58">
+        <v>24.18</v>
+      </c>
+      <c r="E11" s="58">
+        <v>24.83</v>
+      </c>
+      <c r="F11" s="58">
+        <v>24.76</v>
+      </c>
+      <c r="G11" s="58">
+        <v>23.72</v>
+      </c>
+      <c r="H11" s="58">
+        <v>22.619999999999997</v>
+      </c>
+      <c r="I11">
+        <v>23.911701065246337</v>
+      </c>
+      <c r="J11">
+        <v>21.983645139813582</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2198,86 +2200,86 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="35.33203125" customWidth="1"/>
-    <col min="2" max="2" width="18.33203125" customWidth="1"/>
+    <col min="1" max="1" width="35.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" customWidth="1"/>
     <col min="3" max="3" width="19" customWidth="1"/>
-    <col min="4" max="4" width="15.1640625" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="32" x14ac:dyDescent="0.2">
-      <c r="A1" s="58" t="s">
-        <v>59</v>
-      </c>
-      <c r="B1" s="55" t="s">
-        <v>51</v>
-      </c>
-      <c r="C1" s="55" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" s="55" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="30">
+      <c r="A1" s="49" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="47" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="47" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="47" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="57">
+        <v>37</v>
+      </c>
+      <c r="B2" s="48">
         <f>'MEX Split'!D3</f>
-        <v>2.6842318085027003E-2</v>
-      </c>
-      <c r="C2" s="57">
+        <v>2.1455557591463146E-2</v>
+      </c>
+      <c r="C2" s="48">
         <f>B2</f>
-        <v>2.6842318085027003E-2</v>
-      </c>
-      <c r="D2" s="57">
+        <v>2.1455557591463146E-2</v>
+      </c>
+      <c r="D2" s="48">
         <f>'MEX Split'!H3</f>
-        <v>0.15861731280438049</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.22575511827891179</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B3" s="57">
+        <v>71</v>
+      </c>
+      <c r="B3" s="48">
         <v>0</v>
       </c>
-      <c r="C3" s="57">
+      <c r="C3" s="48">
         <f t="shared" ref="C3:C5" si="0">B3</f>
         <v>0</v>
       </c>
-      <c r="D3" s="57">
+      <c r="D3" s="48">
         <f>'MEX Split'!H4</f>
-        <v>0.5583491101171203</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.7742448817210883</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B4" s="57">
+        <v>72</v>
+      </c>
+      <c r="B4" s="48">
         <f>'MEX Split'!D4</f>
-        <v>0.97315768191497298</v>
-      </c>
-      <c r="C4" s="57">
+        <v>0.97854444240853677</v>
+      </c>
+      <c r="C4" s="48">
         <f t="shared" si="0"/>
-        <v>0.97315768191497298</v>
+        <v>0.97854444240853677</v>
       </c>
       <c r="D4">
         <f>Commercial!C22</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
-      <c r="C5" s="56">
+      <c r="C5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2289,4 +2291,175 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
+    <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="79748b23-d81a-423e-9112-21109dc864e6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A71FCF8-E967-4369-911D-2673EEB78B21}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0975397-097C-44D3-9C92-87919ED8E173}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98B13E72-6037-435B-8C2E-B6451D881DDE}"/>
 </file>